--- a/research/traditional_assets/database/data/spain/spain_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_insurance_prop_cas.xlsx
@@ -588,82 +588,85 @@
         </is>
       </c>
       <c r="F2">
-        <v>-0.028</v>
+        <v>0.016</v>
       </c>
       <c r="G2">
-        <v>0.209991611520179</v>
+        <v>0.1995317654570608</v>
       </c>
       <c r="H2">
-        <v>0.209991611520179</v>
+        <v>0.1995317654570608</v>
       </c>
       <c r="I2">
-        <v>0.1747599962717867</v>
+        <v>0.1280195807172502</v>
       </c>
       <c r="J2">
-        <v>0.1312563085005051</v>
+        <v>0.09808344302101107</v>
       </c>
       <c r="K2">
-        <v>140.9</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="L2">
-        <v>0.1313263118650387</v>
+        <v>0.08577205491114184</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>21.756</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.01813453363340835</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.2699255583126551</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>21.756</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.01813453363340835</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.2699255583126551</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>0.06876719179794949</v>
       </c>
       <c r="X2">
-        <v>0.06338178771555626</v>
+        <v>0.09888324157332615</v>
       </c>
       <c r="AB2">
-        <v>0.06125679790092471</v>
+        <v>0.09888324157332615</v>
       </c>
       <c r="AD2">
-        <v>151.4</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>151.4</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>151.4</v>
+        <v>-82.5</v>
       </c>
       <c r="AH2">
-        <v>0.07098982510432786</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>0.2538990441053162</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>0.07098982510432786</v>
+        <v>-0.0738453276047261</v>
       </c>
       <c r="AK2">
-        <v>0.2538990441053162</v>
+        <v>-0.394359464627151</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -672,10 +675,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>0.7844559585492228</v>
+        <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.7844559585492228</v>
+        <v>-0.6637168141592921</v>
       </c>
     </row>
     <row r="3">
@@ -695,82 +698,85 @@
         </is>
       </c>
       <c r="F3">
-        <v>-0.028</v>
+        <v>0.016</v>
       </c>
       <c r="G3">
-        <v>0.209991611520179</v>
+        <v>0.1995317654570608</v>
       </c>
       <c r="H3">
-        <v>0.209991611520179</v>
+        <v>0.1995317654570608</v>
       </c>
       <c r="I3">
-        <v>0.1747599962717867</v>
+        <v>0.1280195807172502</v>
       </c>
       <c r="J3">
-        <v>0.1312563085005051</v>
+        <v>0.09808344302101107</v>
       </c>
       <c r="K3">
-        <v>140.9</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="L3">
-        <v>0.1313263118650387</v>
+        <v>0.08577205491114184</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>21.756</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.01813453363340835</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.2699255583126551</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>21.756</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.01813453363340835</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.2699255583126551</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.06876719179794949</v>
       </c>
       <c r="X3">
-        <v>0.06338178771555626</v>
+        <v>0.09888324157332615</v>
       </c>
       <c r="AB3">
-        <v>0.06125679790092471</v>
+        <v>0.09888324157332615</v>
       </c>
       <c r="AD3">
-        <v>151.4</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>151.4</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>151.4</v>
+        <v>-82.5</v>
       </c>
       <c r="AH3">
-        <v>0.07098982510432786</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.2538990441053162</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.07098982510432786</v>
+        <v>-0.0738453276047261</v>
       </c>
       <c r="AK3">
-        <v>0.2538990441053162</v>
+        <v>-0.394359464627151</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -779,10 +785,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.7844559585492228</v>
+        <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.7844559585492228</v>
+        <v>-0.6637168141592921</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/spain/spain_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_insurance_prop_cas.xlsx
@@ -588,97 +588,118 @@
         </is>
       </c>
       <c r="F2">
-        <v>0.016</v>
+        <v>0.0562</v>
       </c>
       <c r="G2">
-        <v>0.1995317654570608</v>
+        <v>0.08434650455927052</v>
       </c>
       <c r="H2">
-        <v>0.1995317654570608</v>
+        <v>0.08434650455927052</v>
       </c>
       <c r="I2">
-        <v>0.1280195807172502</v>
+        <v>-0.006439969604863222</v>
       </c>
       <c r="J2">
-        <v>0.09808344302101107</v>
+        <v>-0.006439969604863222</v>
       </c>
       <c r="K2">
-        <v>80.59999999999999</v>
+        <v>-6.82</v>
       </c>
       <c r="L2">
-        <v>0.08577205491114184</v>
+        <v>-0.006477963525835867</v>
       </c>
       <c r="M2">
-        <v>21.756</v>
+        <v>34.004</v>
       </c>
       <c r="N2">
-        <v>0.01813453363340835</v>
+        <v>0.03322974689729307</v>
       </c>
       <c r="O2">
-        <v>0.2699255583126551</v>
+        <v>-4.985923753665689</v>
       </c>
       <c r="P2">
-        <v>21.756</v>
+        <v>33.5</v>
       </c>
       <c r="Q2">
-        <v>0.01813453363340835</v>
+        <v>0.03273722271083749</v>
       </c>
       <c r="R2">
-        <v>0.2699255583126551</v>
+        <v>-4.912023460410557</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.5039999999999978</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.01482178567227379</v>
       </c>
       <c r="U2">
-        <v>82.5</v>
+        <v>43.8</v>
       </c>
       <c r="V2">
-        <v>0.06876719179794949</v>
+        <v>0.04280269715625916</v>
+      </c>
+      <c r="W2">
+        <v>-0.01983134632160512</v>
       </c>
       <c r="X2">
-        <v>0.09888324157332615</v>
+        <v>0.08472153929946491</v>
+      </c>
+      <c r="Y2">
+        <v>-0.10455288562107</v>
+      </c>
+      <c r="Z2">
+        <v>3.352866242038216</v>
+      </c>
+      <c r="AA2">
+        <v>-0.02159235668789809</v>
       </c>
       <c r="AB2">
-        <v>0.09888324157332615</v>
+        <v>0.08460124952739843</v>
+      </c>
+      <c r="AC2">
+        <v>-0.1061936062152965</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AG2">
-        <v>-82.5</v>
+        <v>-40.54</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.003175654613466334</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>0.01005676209279368</v>
       </c>
       <c r="AJ2">
-        <v>-0.0738453276047261</v>
+        <v>-0.04125117017379624</v>
       </c>
       <c r="AK2">
-        <v>-0.394359464627151</v>
+        <v>-0.1445998002568127</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>-1.621890547263682</v>
+      </c>
+      <c r="AO2">
+        <v>-4.774647887323944</v>
       </c>
       <c r="AP2">
-        <v>-0.6637168141592921</v>
+        <v>20.16915422885572</v>
+      </c>
+      <c r="AQ2">
+        <v>-4.774647887323944</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Línea Directa Aseguradora, S.A. (BME:LDA)</t>
+          <t>Línea Directa Aseguradora, S.A., Compañía de Seguros y Reaseguros (BME:LDA)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -698,97 +719,118 @@
         </is>
       </c>
       <c r="F3">
-        <v>0.016</v>
+        <v>0.0562</v>
       </c>
       <c r="G3">
-        <v>0.1995317654570608</v>
+        <v>0.08434650455927052</v>
       </c>
       <c r="H3">
-        <v>0.1995317654570608</v>
+        <v>0.08434650455927052</v>
       </c>
       <c r="I3">
-        <v>0.1280195807172502</v>
+        <v>-0.006439969604863222</v>
       </c>
       <c r="J3">
-        <v>0.09808344302101107</v>
+        <v>-0.006439969604863222</v>
       </c>
       <c r="K3">
-        <v>80.59999999999999</v>
+        <v>-6.82</v>
       </c>
       <c r="L3">
-        <v>0.08577205491114184</v>
+        <v>-0.006477963525835867</v>
       </c>
       <c r="M3">
-        <v>21.756</v>
+        <v>34.004</v>
       </c>
       <c r="N3">
-        <v>0.01813453363340835</v>
+        <v>0.03322974689729307</v>
       </c>
       <c r="O3">
-        <v>0.2699255583126551</v>
+        <v>-4.985923753665689</v>
       </c>
       <c r="P3">
-        <v>21.756</v>
+        <v>33.5</v>
       </c>
       <c r="Q3">
-        <v>0.01813453363340835</v>
+        <v>0.03273722271083749</v>
       </c>
       <c r="R3">
-        <v>0.2699255583126551</v>
+        <v>-4.912023460410557</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.5039999999999978</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.01482178567227379</v>
       </c>
       <c r="U3">
-        <v>82.5</v>
+        <v>43.8</v>
       </c>
       <c r="V3">
-        <v>0.06876719179794949</v>
+        <v>0.04280269715625916</v>
+      </c>
+      <c r="W3">
+        <v>-0.01983134632160512</v>
       </c>
       <c r="X3">
-        <v>0.09888324157332615</v>
+        <v>0.08472153929946491</v>
+      </c>
+      <c r="Y3">
+        <v>-0.10455288562107</v>
+      </c>
+      <c r="Z3">
+        <v>3.352866242038216</v>
+      </c>
+      <c r="AA3">
+        <v>-0.02159235668789809</v>
       </c>
       <c r="AB3">
-        <v>0.09888324157332615</v>
+        <v>0.08460124952739843</v>
+      </c>
+      <c r="AC3">
+        <v>-0.1061936062152965</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AG3">
-        <v>-82.5</v>
+        <v>-40.54</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.003175654613466334</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.01005676209279368</v>
       </c>
       <c r="AJ3">
-        <v>-0.0738453276047261</v>
+        <v>-0.04125117017379624</v>
       </c>
       <c r="AK3">
-        <v>-0.394359464627151</v>
+        <v>-0.1445998002568127</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>-1.621890547263682</v>
+      </c>
+      <c r="AO3">
+        <v>-4.774647887323944</v>
       </c>
       <c r="AP3">
-        <v>-0.6637168141592921</v>
+        <v>20.16915422885572</v>
+      </c>
+      <c r="AQ3">
+        <v>-4.774647887323944</v>
       </c>
     </row>
   </sheetData>
